--- a/templates/tpl_booking_mssnhsjl9u3s.xlsx
+++ b/templates/tpl_booking_mssnhsjl9u3s.xlsx
@@ -352,6 +352,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1718,5 +1767,6 @@
     <mergeCell ref="H93:I93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/templates/tpl_booking_mssnhsjl9u3s.xlsx
+++ b/templates/tpl_booking_mssnhsjl9u3s.xlsx
@@ -322,21 +322,576 @@
       <patternFill/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="70">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="medium"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="hair"/>
+      <top style="thin"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF99CCFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair"/>
+      <top style="thin"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top style="thin"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="hair"/>
+      <top/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair"/>
+      <top/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right/>
+      <top/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="hair"/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair"/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="hair"/>
+      <top style="hair"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair"/>
+      <top style="hair"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right/>
+      <top style="hair"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="hair"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top style="hair"/>
+      <bottom style="thin">
+        <color rgb="FF99CCFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="medium"/>
+      <top style="hair"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top style="hair"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -720,15 +1275,16 @@
       <c r="H1"/>
       <c r="I1"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1" spans="7:9" x14ac:dyDescent="0.25">
-      <c r="G2" t="s">
+    <row r="2" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="G2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
     </row>
     <row r="3" ht="15.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B3"/>
@@ -741,10 +1297,14 @@
       <c r="I3"/>
     </row>
     <row r="4" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F4" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8" t="s">
         <v>4</v>
       </c>
       <c r="G4"/>
@@ -752,125 +1312,164 @@
       <c r="I4"/>
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E5" s="10"/>
+      <c r="F5" s="11" t="s">
         <v>0</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" ht="22.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F6" t="s">
+      <c r="E6" s="10"/>
+      <c r="F6" s="12" t="s">
         <v>7</v>
       </c>
       <c r="G6"/>
       <c r="H6"/>
-    </row>
-    <row r="7" ht="12" customHeight="1" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F7" t="s">
+      <c r="I6" s="13"/>
+    </row>
+    <row r="7" ht="12" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="15" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G8" t="s">
+      <c r="I7" s="16"/>
+    </row>
+    <row r="8" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="19" t="s">
         <v>12</v>
       </c>
+      <c r="I8" s="20"/>
     </row>
     <row r="9" ht="17.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F9" t="s">
+      <c r="E9" s="10"/>
+      <c r="F9" s="9" t="s">
         <v>14</v>
       </c>
+      <c r="I9" s="3"/>
       <c r="J9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F10" t="s">
+    <row r="10" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="9"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="9" t="s">
         <v>16</v>
       </c>
+      <c r="I10" s="3"/>
       <c r="J10"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F11" t="s">
+    <row r="11" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="9"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="9" t="s">
         <v>17</v>
       </c>
       <c r="H11" t="s">
         <v>18</v>
       </c>
+      <c r="I11" s="3"/>
       <c r="J11"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
+    <row r="12" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="9" t="s">
         <v>19</v>
       </c>
       <c r="H12" t="s">
         <v>20</v>
       </c>
+      <c r="I12" s="3"/>
       <c r="J12"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="5"/>
       <c r="H13"/>
+      <c r="I13" s="7"/>
       <c r="J13"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F14" t="s">
+      <c r="E14" s="10"/>
+      <c r="F14" s="24" t="s">
         <v>23</v>
       </c>
+      <c r="G14" s="9"/>
       <c r="H14"/>
+      <c r="I14" s="10"/>
       <c r="J14"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F15" t="s">
+      <c r="E15" s="10"/>
+      <c r="F15" s="25" t="s">
         <v>25</v>
       </c>
+      <c r="G15" s="17"/>
       <c r="H15"/>
+      <c r="I15" s="22"/>
       <c r="J15"/>
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F16" t="s">
+      <c r="E16" s="10"/>
+      <c r="F16" s="25" t="s">
         <v>3</v>
       </c>
       <c r="G16"/>
-      <c r="H16" t="s">
+      <c r="H16" s="26" t="s">
         <v>27</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="E17" s="10"/>
       <c r="F17"/>
       <c r="G17"/>
       <c r="H17"/>
@@ -878,164 +1477,193 @@
       <c r="J17"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="F18" t="s">
+      <c r="E18" s="22"/>
+      <c r="F18" s="28" t="s">
         <v>30</v>
       </c>
       <c r="G18"/>
+      <c r="H18" s="29"/>
       <c r="I18"/>
       <c r="J18"/>
     </row>
     <row r="19" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F19" t="s">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="29" t="s">
         <v>32</v>
       </c>
       <c r="G19"/>
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" ht="12.75" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="20" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="9"/>
+      <c r="E20" s="10"/>
       <c r="F20"/>
       <c r="G20"/>
       <c r="H20"/>
       <c r="I20"/>
     </row>
     <row r="21" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="E21" s="10"/>
       <c r="F21"/>
       <c r="G21"/>
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" ht="12.75" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="22" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="E22" s="10"/>
       <c r="F22"/>
       <c r="G22"/>
       <c r="H22"/>
       <c r="I22"/>
     </row>
     <row r="23" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="E23" s="10"/>
       <c r="F23"/>
       <c r="G23"/>
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" ht="12.75" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="24" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="E24" s="10"/>
       <c r="F24"/>
       <c r="G24"/>
       <c r="H24"/>
       <c r="I24"/>
     </row>
-    <row r="25" ht="12.75" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="25" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="E25" s="10"/>
       <c r="F25"/>
       <c r="G25"/>
       <c r="H25"/>
       <c r="I25"/>
     </row>
-    <row r="26" ht="13.5" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="26" ht="13.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="E26" s="10"/>
       <c r="F26"/>
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26"/>
     </row>
     <row r="27" ht="15.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="30" t="s">
         <v>33</v>
       </c>
       <c r="B27"/>
-      <c r="C27" t="s">
+      <c r="C27" s="31" t="s">
         <v>34</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
-      <c r="F27" t="s">
+      <c r="F27" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="33" t="s">
         <v>24</v>
       </c>
       <c r="I27"/>
     </row>
     <row r="28" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="27" t="s">
         <v>35</v>
       </c>
       <c r="B28"/>
-      <c r="C28" t="s">
+      <c r="C28" s="24" t="s">
         <v>36</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
-      <c r="F28" t="s">
+      <c r="F28" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="11" t="s">
         <v>24</v>
       </c>
       <c r="I28"/>
     </row>
-    <row r="29" ht="18.75" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="29" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="C29" s="9"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="26"/>
       <c r="I29"/>
     </row>
-    <row r="30" ht="18.75" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="30" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="27"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="22"/>
       <c r="F30"/>
       <c r="G30"/>
       <c r="H30"/>
       <c r="I30"/>
     </row>
     <row r="31" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="32" t="s">
         <v>40</v>
       </c>
       <c r="D31"/>
       <c r="E31"/>
       <c r="F31"/>
-      <c r="G31" t="s">
+      <c r="G31" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="35" t="s">
         <v>42</v>
       </c>
       <c r="I31"/>
     </row>
     <row r="32" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="38" t="s">
         <v>45</v>
       </c>
       <c r="D32"/>
       <c r="E32"/>
       <c r="F32"/>
-      <c r="G32" t="s">
+      <c r="G32" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="40" t="s">
         <v>47</v>
       </c>
       <c r="I32"/>
@@ -1059,13 +1687,13 @@
       <c r="F33" t="s">
         <v>50</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="3" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1094,7 +1722,7 @@
       <c r="H34" t="s">
         <v>52</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" s="3" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1123,69 +1751,131 @@
       <c r="H35" t="s">
         <v>52</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="3" t="s">
         <v>52</v>
       </c>
       <c r="J35"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I36" s="3"/>
       <c r="J36"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I37" s="3"/>
       <c r="J37"/>
     </row>
-    <row r="38" ht="14.25" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="38" ht="14.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="I38" s="3"/>
       <c r="J38"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="I39" s="3"/>
       <c r="J39"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="I40" s="3"/>
       <c r="J40"/>
     </row>
-    <row r="41" ht="14.25" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="41" ht="14.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="I41" s="3"/>
       <c r="J41"/>
     </row>
-    <row r="42" ht="14.25" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="42" ht="14.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="27"/>
+      <c r="B42" s="19"/>
+      <c r="I42" s="3"/>
       <c r="J42"/>
     </row>
-    <row r="43" ht="14.25" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="43" ht="14.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="42"/>
+      <c r="B43" s="43"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="13"/>
       <c r="J43"/>
     </row>
-    <row r="44" ht="14.25" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="44" ht="14.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="44"/>
+      <c r="B44" s="45"/>
+      <c r="E44" s="46"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="49"/>
       <c r="J44"/>
     </row>
-    <row r="45" ht="14.25" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="45" ht="14.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="50"/>
+      <c r="B45" s="45"/>
+      <c r="E45" s="51"/>
+      <c r="G45" s="47"/>
+      <c r="H45" s="52"/>
+      <c r="I45" s="53"/>
       <c r="J45"/>
     </row>
-    <row r="46" ht="12.75" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="46" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="50"/>
+      <c r="B46" s="45"/>
+      <c r="E46" s="51"/>
+      <c r="G46" s="47"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="53"/>
       <c r="J46"/>
     </row>
-    <row r="47" ht="12.75" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="47" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="54"/>
+      <c r="B47" s="45"/>
+      <c r="E47" s="55"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="56"/>
+      <c r="I47" s="57"/>
       <c r="J47"/>
     </row>
-    <row r="48" ht="12.75" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="48" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="54"/>
+      <c r="B48" s="45"/>
+      <c r="E48" s="55"/>
+      <c r="G48" s="47"/>
+      <c r="H48" s="56"/>
+      <c r="I48" s="57"/>
       <c r="J48"/>
     </row>
     <row r="49" ht="13.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="54" t="s">
         <v>53</v>
       </c>
+      <c r="B49" s="45"/>
+      <c r="E49" s="55"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
       <c r="J49"/>
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="58" t="s">
         <v>54</v>
       </c>
+      <c r="B50" s="45"/>
+      <c r="E50" s="59"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="60"/>
+      <c r="I50" s="61"/>
       <c r="J50"/>
     </row>
     <row r="51" ht="39" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="A51" s="62" t="s">
         <v>55</v>
       </c>
       <c r="B51"/>
       <c r="C51"/>
-      <c r="E51" t="s">
+      <c r="E51" s="57" t="s">
         <v>56</v>
       </c>
       <c r="F51"/>
@@ -1195,38 +1885,44 @@
       <c r="J51"/>
     </row>
     <row r="52" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="A52" s="58" t="s">
         <v>57</v>
       </c>
+      <c r="B52" s="45"/>
+      <c r="E52" s="59"/>
+      <c r="G52" s="47"/>
+      <c r="H52" s="60"/>
+      <c r="I52" s="61"/>
       <c r="J52"/>
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="A53" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="45" t="s">
         <v>59</v>
       </c>
       <c r="C53" t="s">
         <v>60</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="59" t="s">
         <v>61</v>
       </c>
       <c r="E53"/>
       <c r="F53" t="s">
         <v>62</v>
       </c>
-      <c r="G53" t="s">
+      <c r="G53" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="H53" t="s">
+      <c r="H53" s="63" t="s">
         <v>64</v>
       </c>
       <c r="I53"/>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B54">
+    <row r="54" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="58"/>
+      <c r="B54" s="45">
         <v>4900228258</v>
       </c>
       <c r="C54" t="s">
@@ -1235,48 +1931,60 @@
       <c r="D54" t="s">
         <v>66</v>
       </c>
+      <c r="E54" s="59"/>
       <c r="F54">
         <v>61</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="47">
         <v>4202220000</v>
       </c>
-    </row>
-    <row r="55" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B55">
+      <c r="H54" s="60"/>
+      <c r="I54" s="61"/>
+    </row>
+    <row r="55" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="58"/>
+      <c r="B55" s="64">
         <v>4900228258</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="F55">
+      <c r="E55" s="59"/>
+      <c r="F55" s="64">
         <v>61</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="64">
         <v>4202220000</v>
       </c>
-    </row>
-    <row r="56" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B56">
+      <c r="H55" s="60"/>
+      <c r="I55" s="61"/>
+    </row>
+    <row r="56" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="30"/>
+      <c r="B56" s="65">
         <v>4900228258</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="F56">
+      <c r="E56" s="65"/>
+      <c r="F56" s="65">
         <v>20</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="65">
         <v>4202220000</v>
       </c>
-    </row>
-    <row r="57" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H56" s="65"/>
+      <c r="I56" s="66"/>
+    </row>
+    <row r="57" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="2"/>
       <c r="B57">
         <v>4900228258</v>
       </c>
@@ -1292,8 +2000,10 @@
       <c r="G57">
         <v>4202220000</v>
       </c>
-    </row>
-    <row r="58" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="I57" s="3"/>
+    </row>
+    <row r="58" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="2"/>
       <c r="B58">
         <v>4900228258</v>
       </c>
@@ -1309,42 +2019,52 @@
       <c r="G58">
         <v>4202220000</v>
       </c>
-    </row>
-    <row r="59" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B59">
+      <c r="I58" s="3"/>
+    </row>
+    <row r="59" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="67"/>
+      <c r="B59" s="68">
         <v>4900228258</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="F59">
+      <c r="E59" s="68"/>
+      <c r="F59" s="68">
         <v>69</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="68">
         <v>4202220000</v>
       </c>
-    </row>
-    <row r="60" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B60">
+      <c r="H59" s="68"/>
+      <c r="I59" s="69"/>
+    </row>
+    <row r="60" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="30"/>
+      <c r="B60" s="65">
         <v>4900228258</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="F60">
+      <c r="E60" s="65"/>
+      <c r="F60" s="65">
         <v>61</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="65">
         <v>4202220000</v>
       </c>
-    </row>
-    <row r="61" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H60" s="65"/>
+      <c r="I60" s="66"/>
+    </row>
+    <row r="61" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="2"/>
       <c r="B61">
         <v>4900228258</v>
       </c>
@@ -1360,8 +2080,10 @@
       <c r="G61">
         <v>4202220000</v>
       </c>
-    </row>
-    <row r="62" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="I61" s="3"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="2"/>
       <c r="B62">
         <v>4900228258</v>
       </c>
@@ -1377,8 +2099,10 @@
       <c r="G62">
         <v>4202220000</v>
       </c>
-    </row>
-    <row r="63" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="I62" s="3"/>
+    </row>
+    <row r="63" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="2"/>
       <c r="B63">
         <v>4900228258</v>
       </c>
@@ -1394,8 +2118,10 @@
       <c r="G63">
         <v>4202220000</v>
       </c>
-    </row>
-    <row r="64" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="I63" s="3"/>
+    </row>
+    <row r="64" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="2"/>
       <c r="B64">
         <v>4900228258</v>
       </c>
@@ -1411,8 +2137,10 @@
       <c r="G64">
         <v>4202220000</v>
       </c>
-    </row>
-    <row r="65" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="I64" s="3"/>
+    </row>
+    <row r="65" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="2"/>
       <c r="B65">
         <v>4900228258</v>
       </c>
@@ -1428,8 +2156,10 @@
       <c r="G65">
         <v>4202220000</v>
       </c>
-    </row>
-    <row r="66" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="I65" s="3"/>
+    </row>
+    <row r="66" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="2"/>
       <c r="B66">
         <v>4900228258</v>
       </c>
@@ -1445,25 +2175,30 @@
       <c r="G66">
         <v>4202220000</v>
       </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B67">
+      <c r="I66" s="3"/>
+    </row>
+    <row r="67" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="67"/>
+      <c r="B67" s="68">
         <v>4900228259</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="F67">
+      <c r="E67" s="68"/>
+      <c r="F67" s="68">
         <v>14</v>
       </c>
-      <c r="G67">
+      <c r="G67" s="68">
         <v>4202220000</v>
       </c>
-    </row>
-    <row r="68" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H67" s="68"/>
+      <c r="I67" s="69"/>
+    </row>
+    <row r="68" ht="15" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>4900228259</v>
       </c>
@@ -1479,6 +2214,8 @@
       <c r="G68">
         <v>4202220000</v>
       </c>
+      <c r="H68" s="65"/>
+      <c r="I68" s="65"/>
     </row>
     <row r="69" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B69">

--- a/templates/tpl_booking_mssnhsjl9u3s.xlsx
+++ b/templates/tpl_booking_mssnhsjl9u3s.xlsx
@@ -322,7 +322,7 @@
       <patternFill/>
     </fill>
   </fills>
-  <borders count="70">
+  <borders count="79">
     <border>
       <left/>
       <right/>
@@ -335,308 +335,342 @@
       <right style="medium"/>
       <top style="medium"/>
       <bottom/>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom/>
     </border>
     <border>
       <left style="medium"/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium"/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium"/>
       <right style="medium"/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="medium"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom/>
     </border>
     <border>
       <left style="thin"/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin"/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="medium"/>
       <top/>
       <bottom style="thin"/>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin"/>
       <right/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left/>
       <right style="medium"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="hair"/>
       <right style="hair"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="hair"/>
       <right/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="hair"/>
       <right style="medium"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right/>
       <top/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="hair"/>
       <right style="hair"/>
       <top/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="hair"/>
       <right/>
       <top/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="hair"/>
       <right style="medium"/>
       <top/>
       <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
       <top/>
       <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="medium"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium"/>
       <right/>
       <top/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="medium"/>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
     </border>
     <border>
       <left style="thin"/>
       <right style="medium"/>
       <top style="thin"/>
       <bottom style="medium"/>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom style="medium"/>
     </border>
     <border>
       <left style="medium"/>
       <right/>
       <top style="medium"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="medium"/>
       <bottom/>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="medium"/>
       <top style="medium"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="hair"/>
       <right style="thin"/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="medium"/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium"/>
       <right/>
       <top/>
       <bottom style="hair"/>
-      <diagonal/>
     </border>
     <border>
       <left style="hair"/>
       <right style="thin"/>
       <top/>
       <bottom style="hair"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top/>
       <bottom style="hair"/>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair"/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="hair"/>
     </border>
     <border>
       <left style="thin"/>
       <right/>
       <top/>
       <bottom style="hair"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="medium"/>
       <top/>
       <bottom style="hair"/>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom style="hair"/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="hair"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium"/>
       <right/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium"/>
       <right style="hair"/>
       <top style="thin"/>
       <bottom style="hair"/>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -645,119 +679,96 @@
       <bottom style="thin">
         <color rgb="FF99CCFF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="hair"/>
       <top style="thin"/>
       <bottom style="hair"/>
-      <diagonal/>
     </border>
     <border>
       <left style="hair"/>
       <right style="hair"/>
       <top style="thin"/>
       <bottom style="hair"/>
-      <diagonal/>
     </border>
     <border>
       <left style="hair"/>
       <right/>
       <top style="thin"/>
       <bottom style="hair"/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium"/>
       <top style="thin"/>
       <bottom style="hair"/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium"/>
       <right style="hair"/>
       <top/>
       <bottom style="hair"/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="hair"/>
       <top/>
       <bottom style="hair"/>
-      <diagonal/>
     </border>
     <border>
       <left style="hair"/>
       <right/>
       <top/>
       <bottom style="hair"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium"/>
-      <top/>
-      <bottom style="hair"/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium"/>
       <right style="hair"/>
       <top style="hair"/>
       <bottom style="hair"/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="hair"/>
       <top style="hair"/>
       <bottom style="hair"/>
-      <diagonal/>
     </border>
     <border>
       <left style="hair"/>
       <right/>
       <top style="hair"/>
       <bottom style="hair"/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium"/>
       <top style="hair"/>
       <bottom style="hair"/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium"/>
       <right style="hair"/>
       <top style="hair"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="hair"/>
       <top style="hair"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="hair"/>
       <right/>
       <top style="hair"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium"/>
       <top style="hair"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium"/>
@@ -766,132 +777,116 @@
       <bottom style="thin">
         <color rgb="FF99CCFF"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="hair"/>
     </border>
     <border>
       <left style="hair"/>
       <right style="medium"/>
       <top style="hair"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="hair"/>
       <right style="hair"/>
       <top style="hair"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium"/>
       <right/>
       <top/>
       <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium"/>
-      <top/>
-      <bottom style="medium"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf applyBorder="1" numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1"/>
+    <xf borderId="2" applyBorder="1"/>
+    <xf borderId="3" applyBorder="1"/>
+    <xf borderId="4" applyBorder="1"/>
+    <xf borderId="5" applyBorder="1"/>
+    <xf borderId="6" applyBorder="1"/>
+    <xf borderId="7" applyBorder="1"/>
+    <xf borderId="8" applyBorder="1"/>
+    <xf borderId="9" applyBorder="1"/>
+    <xf borderId="10" applyBorder="1"/>
+    <xf borderId="11" applyBorder="1"/>
+    <xf borderId="12" applyBorder="1"/>
+    <xf borderId="13" applyBorder="1"/>
+    <xf borderId="14" applyBorder="1"/>
+    <xf borderId="15" applyBorder="1"/>
+    <xf borderId="16" applyBorder="1"/>
+    <xf borderId="17" applyBorder="1"/>
+    <xf borderId="18" applyBorder="1"/>
+    <xf borderId="19" applyBorder="1"/>
+    <xf borderId="20" applyBorder="1"/>
+    <xf borderId="21" applyBorder="1"/>
+    <xf borderId="22" applyBorder="1"/>
+    <xf borderId="23" applyBorder="1"/>
+    <xf borderId="24" applyBorder="1"/>
+    <xf borderId="25" applyBorder="1"/>
+    <xf borderId="26" applyBorder="1"/>
+    <xf borderId="27" applyBorder="1"/>
+    <xf borderId="28" applyBorder="1"/>
+    <xf borderId="29" applyBorder="1"/>
+    <xf borderId="30" applyBorder="1"/>
+    <xf borderId="31" applyBorder="1"/>
+    <xf borderId="32" applyBorder="1"/>
+    <xf borderId="33" applyBorder="1"/>
+    <xf borderId="34" applyBorder="1"/>
+    <xf borderId="35" applyBorder="1"/>
+    <xf borderId="36" applyBorder="1"/>
+    <xf borderId="37" applyBorder="1"/>
+    <xf borderId="38" applyBorder="1"/>
+    <xf borderId="39" applyBorder="1"/>
+    <xf borderId="40" applyBorder="1"/>
+    <xf borderId="41" applyBorder="1"/>
+    <xf borderId="42" applyBorder="1"/>
+    <xf borderId="43" applyBorder="1"/>
+    <xf borderId="44" applyBorder="1"/>
+    <xf borderId="45" applyBorder="1"/>
+    <xf borderId="46" applyBorder="1"/>
+    <xf borderId="47" applyBorder="1"/>
+    <xf borderId="48" applyBorder="1"/>
+    <xf borderId="49" applyBorder="1"/>
+    <xf borderId="50" applyBorder="1"/>
+    <xf borderId="51" applyBorder="1"/>
+    <xf borderId="52" applyBorder="1"/>
+    <xf borderId="53" applyBorder="1"/>
+    <xf borderId="54" applyBorder="1"/>
+    <xf borderId="55" applyBorder="1"/>
+    <xf borderId="56" applyBorder="1"/>
+    <xf borderId="57" applyBorder="1"/>
+    <xf borderId="58" applyBorder="1"/>
+    <xf borderId="59" applyBorder="1"/>
+    <xf borderId="60" applyBorder="1"/>
+    <xf borderId="61" applyBorder="1"/>
+    <xf borderId="62" applyBorder="1"/>
+    <xf borderId="63" applyBorder="1"/>
+    <xf borderId="64" applyBorder="1"/>
+    <xf borderId="65" applyBorder="1"/>
+    <xf borderId="66" applyBorder="1"/>
+    <xf borderId="67" applyBorder="1"/>
+    <xf borderId="68" applyBorder="1"/>
+    <xf borderId="69" applyBorder="1"/>
+    <xf borderId="70" applyBorder="1"/>
+    <xf borderId="71" applyBorder="1"/>
+    <xf borderId="72" applyBorder="1"/>
+    <xf borderId="73" applyBorder="1"/>
+    <xf borderId="74" applyBorder="1"/>
+    <xf borderId="75" applyBorder="1"/>
+    <xf borderId="76" applyBorder="1"/>
+    <xf borderId="77" applyBorder="1"/>
+    <xf borderId="78" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1263,28 +1258,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="39.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1"/>
-      <c r="C1"/>
-      <c r="D1"/>
-      <c r="E1"/>
-      <c r="F1"/>
-      <c r="G1"/>
-      <c r="H1"/>
-      <c r="I1"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="G2" s="3" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="4"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="G2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="H2"/>
-      <c r="I2"/>
+      <c r="I2" s="6"/>
     </row>
     <row r="3" ht="15.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B3"/>
@@ -1294,379 +1289,379 @@
       <c r="F3"/>
       <c r="G3"/>
       <c r="H3"/>
-      <c r="I3"/>
+      <c r="I3" s="6"/>
     </row>
     <row r="4" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="10"/>
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G4"/>
-      <c r="H4"/>
-      <c r="I4"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="12"/>
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="E5" s="14"/>
+      <c r="A5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="G5"/>
-      <c r="H5"/>
-      <c r="I5"/>
-    </row>
-    <row r="6" ht="22.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E6" s="14"/>
+      <c r="I6" s="20"/>
+      <c r="A6" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="G6"/>
-      <c r="H6"/>
-      <c r="I6" s="13"/>
-    </row>
-    <row r="7" ht="12" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="9" t="s">
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+    </row>
+    <row r="7" ht="12" customHeight="1" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="13"/>
+      <c r="E7" s="14"/>
+      <c r="I7" s="23"/>
+      <c r="F7" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="16"/>
-    </row>
-    <row r="8" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="18" t="s">
+    </row>
+    <row r="8" ht="12.75" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="24"/>
+      <c r="I8" s="27"/>
+      <c r="G8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="20"/>
     </row>
     <row r="9" ht="17.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="E9" s="14"/>
+      <c r="I9" s="6"/>
+      <c r="A9" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="3"/>
       <c r="J9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="9" t="s">
+    <row r="10" ht="15" customHeight="1" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="13"/>
+      <c r="E10" s="14"/>
+      <c r="I10" s="6"/>
+      <c r="F10" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="I10" s="3"/>
       <c r="J10"/>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="9" t="s">
+    <row r="11" ht="15" customHeight="1" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="E11" s="14"/>
+      <c r="I11" s="6"/>
+      <c r="F11" s="13" t="s">
         <v>17</v>
       </c>
       <c r="H11" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="3"/>
       <c r="J11"/>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="9" t="s">
+    <row r="12" ht="15" customHeight="1" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="24"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="28"/>
+      <c r="I12" s="6"/>
+      <c r="F12" s="13" t="s">
         <v>19</v>
       </c>
       <c r="H12" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="3"/>
       <c r="J12"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="8"/>
+      <c r="I13" s="10"/>
+      <c r="A13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="5"/>
-      <c r="H13"/>
-      <c r="I13" s="7"/>
+      <c r="H13" s="9"/>
       <c r="J13"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="E14" s="14"/>
+      <c r="G14" s="13"/>
+      <c r="I14" s="14"/>
+      <c r="A14" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="24" t="s">
+      <c r="F14" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="9"/>
       <c r="H14"/>
-      <c r="I14" s="10"/>
       <c r="J14"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="E15" s="14"/>
+      <c r="G15" s="24"/>
+      <c r="I15" s="28"/>
+      <c r="A15" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="10"/>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="G15" s="17"/>
-      <c r="H15"/>
-      <c r="I15" s="22"/>
+      <c r="H15" s="16"/>
       <c r="J15"/>
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="E16" s="14"/>
+      <c r="A16" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="10"/>
-      <c r="F16" s="25" t="s">
+      <c r="F16" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="G16"/>
-      <c r="H16" s="26" t="s">
+      <c r="G16" s="10"/>
+      <c r="H16" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="I16"/>
+      <c r="I16" s="12"/>
       <c r="J16"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="E17" s="14"/>
+      <c r="A17" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="10"/>
-      <c r="F17"/>
-      <c r="G17"/>
-      <c r="H17"/>
-      <c r="I17"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="17"/>
       <c r="J17"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+      <c r="E18" s="28"/>
+      <c r="H18" s="36"/>
+      <c r="A18" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="28" t="s">
+      <c r="F18" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="G18"/>
-      <c r="H18" s="29"/>
-      <c r="I18"/>
+      <c r="G18" s="35"/>
+      <c r="I18" s="37"/>
       <c r="J18"/>
     </row>
     <row r="19" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="10"/>
+      <c r="A19" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="29" t="s">
+      <c r="F19" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="G19"/>
-      <c r="H19"/>
-      <c r="I19"/>
-    </row>
-    <row r="20" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="E20" s="10"/>
-      <c r="F20"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="12"/>
+    </row>
+    <row r="20" ht="12.75" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="13"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="13"/>
       <c r="G20"/>
       <c r="H20"/>
-      <c r="I20"/>
+      <c r="I20" s="6"/>
     </row>
     <row r="21" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="E21" s="14"/>
+      <c r="A21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="10"/>
-      <c r="F21"/>
+      <c r="F21" s="13"/>
       <c r="G21"/>
       <c r="H21"/>
-      <c r="I21"/>
-    </row>
-    <row r="22" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="E22" s="10"/>
-      <c r="F22"/>
+      <c r="I21" s="6"/>
+    </row>
+    <row r="22" ht="12.75" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="13"/>
       <c r="G22"/>
       <c r="H22"/>
-      <c r="I22"/>
+      <c r="I22" s="6"/>
     </row>
     <row r="23" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="E23" s="14"/>
+      <c r="A23" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="10"/>
-      <c r="F23"/>
+      <c r="F23" s="13"/>
       <c r="G23"/>
       <c r="H23"/>
-      <c r="I23"/>
-    </row>
-    <row r="24" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="E24" s="10"/>
-      <c r="F24"/>
+      <c r="I23" s="6"/>
+    </row>
+    <row r="24" ht="12.75" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="13"/>
       <c r="G24"/>
       <c r="H24"/>
-      <c r="I24"/>
-    </row>
-    <row r="25" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="E25" s="10"/>
-      <c r="F25"/>
+      <c r="I24" s="6"/>
+    </row>
+    <row r="25" ht="12.75" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="13"/>
       <c r="G25"/>
       <c r="H25"/>
-      <c r="I25"/>
-    </row>
-    <row r="26" ht="13.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="E26" s="10"/>
-      <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
-      <c r="I26"/>
+      <c r="I25" s="6"/>
+    </row>
+    <row r="26" ht="13.5" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="40"/>
     </row>
     <row r="27" ht="15.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="B27"/>
-      <c r="C27" s="31" t="s">
+      <c r="B27" s="3"/>
+      <c r="C27" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="D27"/>
-      <c r="E27"/>
-      <c r="F27" s="32" t="s">
+      <c r="D27" s="3"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="G27" s="32" t="s">
+      <c r="G27" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="H27" s="33" t="s">
+      <c r="H27" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="I27"/>
+      <c r="I27" s="4"/>
     </row>
     <row r="28" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="B28"/>
-      <c r="C28" s="24" t="s">
+      <c r="B28" s="16"/>
+      <c r="C28" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28" s="24" t="s">
+      <c r="D28" s="16"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G28" s="24" t="s">
+      <c r="G28" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I28"/>
-    </row>
-    <row r="29" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="C29" s="9"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="26"/>
-      <c r="I29"/>
-    </row>
-    <row r="30" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="27"/>
-      <c r="B30" s="21"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="22"/>
-      <c r="F30"/>
-      <c r="G30"/>
-      <c r="H30"/>
-      <c r="I30"/>
+      <c r="I28" s="17"/>
+    </row>
+    <row r="29" ht="18.75" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="C29" s="13"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="12"/>
+    </row>
+    <row r="30" ht="18.75" customHeight="1" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="33"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="17"/>
     </row>
     <row r="31" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="44" t="s">
         <v>40</v>
       </c>
       <c r="D31"/>
       <c r="E31"/>
-      <c r="F31"/>
-      <c r="G31" s="9" t="s">
+      <c r="F31" s="14"/>
+      <c r="G31" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H31" s="35" t="s">
+      <c r="H31" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="I31"/>
+      <c r="I31" s="6"/>
     </row>
     <row r="32" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="36" t="s">
+      <c r="A32" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="F32"/>
-      <c r="G32" s="39" t="s">
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="H32" s="40" t="s">
+      <c r="H32" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="I32"/>
+      <c r="I32" s="55"/>
     </row>
     <row r="33" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
@@ -1687,13 +1682,13 @@
       <c r="F33" t="s">
         <v>50</v>
       </c>
-      <c r="G33" s="41" t="s">
+      <c r="G33" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="H33" s="41" t="s">
+      <c r="H33" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="I33" s="6" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1722,7 +1717,7 @@
       <c r="H34" t="s">
         <v>52</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="I34" s="6" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1751,178 +1746,181 @@
       <c r="H35" t="s">
         <v>52</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="I35" s="6" t="s">
         <v>52</v>
       </c>
       <c r="J35"/>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="9:10" x14ac:dyDescent="0.25">
-      <c r="I36" s="3"/>
+    <row r="36" ht="15" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="I36" s="6"/>
       <c r="J36"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="9:10" x14ac:dyDescent="0.25">
-      <c r="I37" s="3"/>
+    <row r="37" ht="15" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="I37" s="6"/>
       <c r="J37"/>
     </row>
-    <row r="38" ht="14.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="I38" s="3"/>
+    <row r="38" ht="14.25" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="5"/>
+      <c r="I38" s="6"/>
       <c r="J38"/>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="I39" s="3"/>
+    <row r="39" ht="15" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
+      <c r="I39" s="6"/>
       <c r="J39"/>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="I40" s="3"/>
+    <row r="40" ht="15" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="5"/>
+      <c r="I40" s="6"/>
       <c r="J40"/>
     </row>
-    <row r="41" ht="14.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
-      <c r="I41" s="3"/>
+    <row r="41" ht="14.25" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="5"/>
+      <c r="I41" s="6"/>
       <c r="J41"/>
     </row>
-    <row r="42" ht="14.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="27"/>
-      <c r="B42" s="19"/>
-      <c r="I42" s="3"/>
+    <row r="42" ht="14.25" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="33"/>
+      <c r="B42" s="26"/>
+      <c r="I42" s="6"/>
       <c r="J42"/>
     </row>
-    <row r="43" ht="14.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="42"/>
-      <c r="B43" s="43"/>
-      <c r="C43" s="43"/>
-      <c r="D43" s="43"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="43"/>
-      <c r="I43" s="13"/>
+    <row r="43" ht="14.25" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="57"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="20"/>
       <c r="J43"/>
     </row>
-    <row r="44" ht="14.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="44"/>
-      <c r="B44" s="45"/>
-      <c r="E44" s="46"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="49"/>
+    <row r="44" ht="14.25" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="58"/>
+      <c r="B44" s="59"/>
+      <c r="E44" s="60"/>
+      <c r="G44" s="61"/>
+      <c r="H44" s="62"/>
+      <c r="I44" s="63"/>
       <c r="J44"/>
     </row>
-    <row r="45" ht="14.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="50"/>
-      <c r="B45" s="45"/>
-      <c r="E45" s="51"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="52"/>
-      <c r="I45" s="53"/>
+    <row r="45" ht="14.25" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="64"/>
+      <c r="B45" s="59"/>
+      <c r="E45" s="65"/>
+      <c r="G45" s="61"/>
+      <c r="H45" s="66"/>
+      <c r="I45" s="55"/>
       <c r="J45"/>
     </row>
-    <row r="46" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="50"/>
-      <c r="B46" s="45"/>
-      <c r="E46" s="51"/>
-      <c r="G46" s="47"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="53"/>
+    <row r="46" ht="12.75" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="64"/>
+      <c r="B46" s="59"/>
+      <c r="E46" s="65"/>
+      <c r="G46" s="61"/>
+      <c r="H46" s="66"/>
+      <c r="I46" s="55"/>
       <c r="J46"/>
     </row>
-    <row r="47" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="54"/>
-      <c r="B47" s="45"/>
-      <c r="E47" s="55"/>
-      <c r="G47" s="47"/>
-      <c r="H47" s="56"/>
-      <c r="I47" s="57"/>
+    <row r="47" ht="12.75" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="67"/>
+      <c r="B47" s="59"/>
+      <c r="E47" s="68"/>
+      <c r="G47" s="61"/>
+      <c r="H47" s="69"/>
+      <c r="I47" s="70"/>
       <c r="J47"/>
     </row>
-    <row r="48" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="54"/>
-      <c r="B48" s="45"/>
-      <c r="E48" s="55"/>
-      <c r="G48" s="47"/>
-      <c r="H48" s="56"/>
-      <c r="I48" s="57"/>
+    <row r="48" ht="12.75" customHeight="1" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="67"/>
+      <c r="B48" s="59"/>
+      <c r="E48" s="68"/>
+      <c r="G48" s="61"/>
+      <c r="H48" s="69"/>
+      <c r="I48" s="70"/>
       <c r="J48"/>
     </row>
     <row r="49" ht="13.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="54" t="s">
+      <c r="B49" s="59"/>
+      <c r="E49" s="68"/>
+      <c r="G49" s="61"/>
+      <c r="H49" s="69"/>
+      <c r="I49" s="70"/>
+      <c r="A49" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="B49" s="45"/>
-      <c r="E49" s="55"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="56"/>
-      <c r="I49" s="57"/>
       <c r="J49"/>
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="58" t="s">
+      <c r="B50" s="59"/>
+      <c r="E50" s="72"/>
+      <c r="G50" s="61"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="74"/>
+      <c r="A50" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="B50" s="45"/>
-      <c r="E50" s="59"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="60"/>
-      <c r="I50" s="61"/>
       <c r="J50"/>
     </row>
     <row r="51" ht="39" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="62" t="s">
+      <c r="A51" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="B51"/>
+      <c r="B51" s="59"/>
       <c r="C51"/>
-      <c r="E51" s="57" t="s">
+      <c r="E51" s="70" t="s">
         <v>56</v>
       </c>
       <c r="F51"/>
-      <c r="G51"/>
-      <c r="H51"/>
-      <c r="I51"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="56"/>
+      <c r="I51" s="74"/>
       <c r="J51"/>
     </row>
     <row r="52" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="58" t="s">
+      <c r="B52" s="59"/>
+      <c r="E52" s="72"/>
+      <c r="G52" s="61"/>
+      <c r="H52" s="73"/>
+      <c r="I52" s="74"/>
+      <c r="A52" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="B52" s="45"/>
-      <c r="E52" s="59"/>
-      <c r="G52" s="47"/>
-      <c r="H52" s="60"/>
-      <c r="I52" s="61"/>
       <c r="J52"/>
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="58" t="s">
+      <c r="A53" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="B53" s="45" t="s">
+      <c r="B53" s="59" t="s">
         <v>59</v>
       </c>
       <c r="C53" t="s">
         <v>60</v>
       </c>
-      <c r="D53" s="59" t="s">
+      <c r="D53" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="E53"/>
+      <c r="E53" s="72"/>
       <c r="F53" t="s">
         <v>62</v>
       </c>
-      <c r="G53" s="47" t="s">
+      <c r="G53" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="H53" s="63" t="s">
+      <c r="H53" s="77" t="s">
         <v>64</v>
       </c>
-      <c r="I53"/>
-    </row>
-    <row r="54" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="58"/>
-      <c r="B54" s="45">
+      <c r="I53" s="74"/>
+    </row>
+    <row r="54" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="71"/>
+      <c r="E54" s="72"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="74"/>
+      <c r="B54" s="59">
         <v>4900228258</v>
       </c>
       <c r="C54" t="s">
@@ -1931,60 +1929,58 @@
       <c r="D54" t="s">
         <v>66</v>
       </c>
-      <c r="E54" s="59"/>
       <c r="F54">
         <v>61</v>
       </c>
-      <c r="G54" s="47">
+      <c r="G54" s="61">
         <v>4202220000</v>
       </c>
-      <c r="H54" s="60"/>
-      <c r="I54" s="61"/>
-    </row>
-    <row r="55" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="58"/>
-      <c r="B55" s="64">
+    </row>
+    <row r="55" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="71"/>
+      <c r="E55" s="72"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="74"/>
+      <c r="B55" s="78">
         <v>4900228258</v>
       </c>
-      <c r="C55" s="60" t="s">
+      <c r="C55" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="D55" s="60" t="s">
+      <c r="D55" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="E55" s="59"/>
-      <c r="F55" s="64">
+      <c r="F55" s="78">
         <v>61</v>
       </c>
-      <c r="G55" s="64">
+      <c r="G55" s="78">
         <v>4202220000</v>
       </c>
-      <c r="H55" s="60"/>
-      <c r="I55" s="61"/>
-    </row>
-    <row r="56" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="30"/>
-      <c r="B56" s="65">
+    </row>
+    <row r="56" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="41"/>
+      <c r="E56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="4"/>
+      <c r="B56" s="3">
         <v>4900228258</v>
       </c>
-      <c r="C56" s="65" t="s">
+      <c r="C56" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D56" s="65" t="s">
+      <c r="D56" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E56" s="65"/>
-      <c r="F56" s="65">
+      <c r="F56" s="3">
         <v>20</v>
       </c>
-      <c r="G56" s="65">
+      <c r="G56" s="3">
         <v>4202220000</v>
       </c>
-      <c r="H56" s="65"/>
-      <c r="I56" s="66"/>
-    </row>
-    <row r="57" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
+    </row>
+    <row r="57" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="5"/>
+      <c r="I57" s="6"/>
       <c r="B57">
         <v>4900228258</v>
       </c>
@@ -2000,10 +1996,10 @@
       <c r="G57">
         <v>4202220000</v>
       </c>
-      <c r="I57" s="3"/>
-    </row>
-    <row r="58" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="2"/>
+    </row>
+    <row r="58" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="5"/>
+      <c r="I58" s="6"/>
       <c r="B58">
         <v>4900228258</v>
       </c>
@@ -2019,52 +2015,52 @@
       <c r="G58">
         <v>4202220000</v>
       </c>
-      <c r="I58" s="3"/>
-    </row>
-    <row r="59" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="67"/>
-      <c r="B59" s="68">
+    </row>
+    <row r="59" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="79"/>
+      <c r="E59" s="39"/>
+      <c r="H59" s="39"/>
+      <c r="I59" s="40"/>
+      <c r="B59" s="39">
         <v>4900228258</v>
       </c>
-      <c r="C59" s="68" t="s">
+      <c r="C59" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="D59" s="68" t="s">
+      <c r="D59" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="E59" s="68"/>
-      <c r="F59" s="68">
+      <c r="F59" s="39">
         <v>69</v>
       </c>
-      <c r="G59" s="68">
+      <c r="G59" s="39">
         <v>4202220000</v>
       </c>
-      <c r="H59" s="68"/>
-      <c r="I59" s="69"/>
-    </row>
-    <row r="60" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="30"/>
-      <c r="B60" s="65">
+    </row>
+    <row r="60" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="41"/>
+      <c r="E60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="4"/>
+      <c r="B60" s="3">
         <v>4900228258</v>
       </c>
-      <c r="C60" s="65" t="s">
+      <c r="C60" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D60" s="65" t="s">
+      <c r="D60" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E60" s="65"/>
-      <c r="F60" s="65">
+      <c r="F60" s="3">
         <v>61</v>
       </c>
-      <c r="G60" s="65">
+      <c r="G60" s="3">
         <v>4202220000</v>
       </c>
-      <c r="H60" s="65"/>
-      <c r="I60" s="66"/>
-    </row>
-    <row r="61" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="2"/>
+    </row>
+    <row r="61" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="5"/>
+      <c r="I61" s="6"/>
       <c r="B61">
         <v>4900228258</v>
       </c>
@@ -2080,10 +2076,10 @@
       <c r="G61">
         <v>4202220000</v>
       </c>
-      <c r="I61" s="3"/>
-    </row>
-    <row r="62" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="2"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="5"/>
+      <c r="I62" s="6"/>
       <c r="B62">
         <v>4900228258</v>
       </c>
@@ -2099,10 +2095,10 @@
       <c r="G62">
         <v>4202220000</v>
       </c>
-      <c r="I62" s="3"/>
-    </row>
-    <row r="63" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="2"/>
+    </row>
+    <row r="63" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="5"/>
+      <c r="I63" s="6"/>
       <c r="B63">
         <v>4900228258</v>
       </c>
@@ -2118,10 +2114,10 @@
       <c r="G63">
         <v>4202220000</v>
       </c>
-      <c r="I63" s="3"/>
-    </row>
-    <row r="64" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="2"/>
+    </row>
+    <row r="64" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="5"/>
+      <c r="I64" s="6"/>
       <c r="B64">
         <v>4900228258</v>
       </c>
@@ -2137,10 +2133,10 @@
       <c r="G64">
         <v>4202220000</v>
       </c>
-      <c r="I64" s="3"/>
-    </row>
-    <row r="65" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="2"/>
+    </row>
+    <row r="65" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="5"/>
+      <c r="I65" s="6"/>
       <c r="B65">
         <v>4900228258</v>
       </c>
@@ -2156,10 +2152,10 @@
       <c r="G65">
         <v>4202220000</v>
       </c>
-      <c r="I65" s="3"/>
-    </row>
-    <row r="66" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="2"/>
+    </row>
+    <row r="66" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="5"/>
+      <c r="I66" s="6"/>
       <c r="B66">
         <v>4900228258</v>
       </c>
@@ -2175,30 +2171,31 @@
       <c r="G66">
         <v>4202220000</v>
       </c>
-      <c r="I66" s="3"/>
-    </row>
-    <row r="67" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="67"/>
-      <c r="B67" s="68">
+    </row>
+    <row r="67" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="79"/>
+      <c r="E67" s="39"/>
+      <c r="H67" s="39"/>
+      <c r="I67" s="40"/>
+      <c r="B67" s="39">
         <v>4900228259</v>
       </c>
-      <c r="C67" s="68" t="s">
+      <c r="C67" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="D67" s="68" t="s">
+      <c r="D67" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68">
+      <c r="F67" s="39">
         <v>14</v>
       </c>
-      <c r="G67" s="68">
+      <c r="G67" s="39">
         <v>4202220000</v>
       </c>
-      <c r="H67" s="68"/>
-      <c r="I67" s="69"/>
-    </row>
-    <row r="68" ht="15" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
       <c r="B68">
         <v>4900228259</v>
       </c>
@@ -2214,8 +2211,6 @@
       <c r="G68">
         <v>4202220000</v>
       </c>
-      <c r="H68" s="65"/>
-      <c r="I68" s="65"/>
     </row>
     <row r="69" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B69">

--- a/templates/tpl_booking_mssnhsjl9u3s.xlsx
+++ b/templates/tpl_booking_mssnhsjl9u3s.xlsx
@@ -806,7 +806,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf applyBorder="1" numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1"/>
@@ -887,6 +887,9 @@
     <xf borderId="76" applyBorder="1"/>
     <xf borderId="77" applyBorder="1"/>
     <xf borderId="78" applyBorder="1"/>
+    <xf applyAlignment="1" borderId="12" applyBorder="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1308,8 +1311,10 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E5" s="14"/>
-      <c r="A5" s="13" t="s">
-        <v>5</v>
+      <c r="A5" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{shipper.address}}</t>
+        </is>
       </c>
       <c r="F5" s="15" t="s">
         <v>0</v>
@@ -1423,8 +1428,10 @@
       <c r="E14" s="14"/>
       <c r="G14" s="13"/>
       <c r="I14" s="14"/>
-      <c r="A14" s="13" t="s">
-        <v>22</v>
+      <c r="A14" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{consignee.address}}</t>
+        </is>
       </c>
       <c r="F14" s="30" t="s">
         <v>23</v>

--- a/templates/tpl_booking_mssnhsjl9u3s.xlsx
+++ b/templates/tpl_booking_mssnhsjl9u3s.xlsx
@@ -806,7 +806,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf applyBorder="1" numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1"/>
@@ -890,6 +890,12 @@
     <xf applyAlignment="1" borderId="12" applyBorder="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf applyAlignment="1" borderId="12" applyBorder="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf borderId="31" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -909,19 +915,14 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="2223849" cy="502920"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -952,7 +953,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1311,13 +1312,15 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E5" s="14"/>
-      <c r="A5" s="80" t="inlineStr">
+      <c r="A5" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">{{shipper.address}}</t>
         </is>
       </c>
-      <c r="F5" s="15" t="s">
-        <v>0</v>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freight Term 運費付款方式：{{cb_payTerm}}</t>
+        </is>
       </c>
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
@@ -1326,11 +1329,11 @@
     <row r="6" ht="22.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E6" s="14"/>
       <c r="I6" s="20"/>
-      <c r="A6" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>7</v>
+      <c r="A6" s="13"/>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trade Term 貿易條款：{{cb_tradeTerm}}</t>
+        </is>
       </c>
       <c r="G6" s="19"/>
       <c r="H6" s="19"/>
@@ -1426,9 +1429,13 @@
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E14" s="14"/>
-      <c r="G14" s="13"/>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{cb_blType}}</t>
+        </is>
+      </c>
       <c r="I14" s="14"/>
-      <c r="A14" s="80" t="inlineStr">
+      <c r="A14" s="81" t="inlineStr">
         <is>
           <t xml:space="preserve">{{consignee.address}}</t>
         </is>
@@ -1454,24 +1461,23 @@
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E16" s="14"/>
-      <c r="A16" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="A16" s="5"/>
       <c r="F16" s="31" t="s">
         <v>3</v>
       </c>
       <c r="G16" s="10"/>
-      <c r="H16" s="32" t="s">
-        <v>27</v>
+      <c r="H16" s="82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{consignee.name}}
+{{consignee.address}}</t>
+        </is>
       </c>
       <c r="I16" s="12"/>
       <c r="J16"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E17" s="14"/>
-      <c r="A17" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="A17" s="5"/>
       <c r="F17" s="24"/>
       <c r="G17" s="28"/>
       <c r="H17" s="24"/>
@@ -1480,10 +1486,12 @@
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E18" s="28"/>
-      <c r="H18" s="36"/>
-      <c r="A18" s="33" t="s">
-        <v>29</v>
-      </c>
+      <c r="H18" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{cb_currency}}</t>
+        </is>
+      </c>
+      <c r="A18" s="33"/>
       <c r="F18" s="34" t="s">
         <v>30</v>
       </c>
@@ -1927,484 +1935,224 @@
       <c r="E54" s="72"/>
       <c r="H54" s="73"/>
       <c r="I54" s="74"/>
-      <c r="B54" s="59">
-        <v>4900228258</v>
-      </c>
-      <c r="C54" t="s">
-        <v>65</v>
-      </c>
-      <c r="D54" t="s">
-        <v>66</v>
-      </c>
-      <c r="F54">
-        <v>61</v>
-      </c>
-      <c r="G54" s="61">
-        <v>4202220000</v>
-      </c>
+      <c r="B54" s="59"/>
+      <c r="C54" s=""/>
+      <c r="D54" s=""/>
+      <c r="F54" s=""/>
+      <c r="G54" s="61"/>
     </row>
     <row r="55" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A55" s="71"/>
       <c r="E55" s="72"/>
       <c r="H55" s="73"/>
       <c r="I55" s="74"/>
-      <c r="B55" s="78">
-        <v>4900228258</v>
-      </c>
-      <c r="C55" s="73" t="s">
-        <v>67</v>
-      </c>
-      <c r="D55" s="73" t="s">
-        <v>66</v>
-      </c>
-      <c r="F55" s="78">
-        <v>61</v>
-      </c>
-      <c r="G55" s="78">
-        <v>4202220000</v>
-      </c>
+      <c r="B55" s="78"/>
+      <c r="C55" s="73"/>
+      <c r="D55" s="73"/>
+      <c r="F55" s="78"/>
+      <c r="G55" s="78"/>
     </row>
     <row r="56" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A56" s="41"/>
       <c r="E56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="4"/>
-      <c r="B56" s="3">
-        <v>4900228258</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F56" s="3">
-        <v>20</v>
-      </c>
-      <c r="G56" s="3">
-        <v>4202220000</v>
-      </c>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
     </row>
     <row r="57" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
       <c r="I57" s="6"/>
-      <c r="B57">
-        <v>4900228258</v>
-      </c>
-      <c r="C57" t="s">
-        <v>69</v>
-      </c>
-      <c r="D57" t="s">
-        <v>66</v>
-      </c>
-      <c r="F57">
-        <v>18</v>
-      </c>
-      <c r="G57">
-        <v>4202220000</v>
-      </c>
+      <c r="B57" s=""/>
+      <c r="C57" s=""/>
+      <c r="D57" s=""/>
+      <c r="F57" s=""/>
+      <c r="G57" s=""/>
     </row>
     <row r="58" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
       <c r="I58" s="6"/>
-      <c r="B58">
-        <v>4900228258</v>
-      </c>
-      <c r="C58" t="s">
-        <v>70</v>
-      </c>
-      <c r="D58" t="s">
-        <v>66</v>
-      </c>
-      <c r="F58">
-        <v>69</v>
-      </c>
-      <c r="G58">
-        <v>4202220000</v>
-      </c>
+      <c r="B58" s=""/>
+      <c r="C58" s=""/>
+      <c r="D58" s=""/>
+      <c r="F58" s=""/>
+      <c r="G58" s=""/>
     </row>
     <row r="59" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A59" s="79"/>
       <c r="E59" s="39"/>
       <c r="H59" s="39"/>
       <c r="I59" s="40"/>
-      <c r="B59" s="39">
-        <v>4900228258</v>
-      </c>
-      <c r="C59" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="D59" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="F59" s="39">
-        <v>69</v>
-      </c>
-      <c r="G59" s="39">
-        <v>4202220000</v>
-      </c>
+      <c r="B59" s="39"/>
+      <c r="C59" s="39"/>
+      <c r="D59" s="39"/>
+      <c r="F59" s="39"/>
+      <c r="G59" s="39"/>
     </row>
     <row r="60" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A60" s="41"/>
       <c r="E60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="4"/>
-      <c r="B60" s="3">
-        <v>4900228258</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F60" s="3">
-        <v>61</v>
-      </c>
-      <c r="G60" s="3">
-        <v>4202220000</v>
-      </c>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
     </row>
     <row r="61" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="I61" s="6"/>
-      <c r="B61">
-        <v>4900228258</v>
-      </c>
-      <c r="C61" t="s">
-        <v>73</v>
-      </c>
-      <c r="D61" t="s">
-        <v>66</v>
-      </c>
-      <c r="F61">
-        <v>45</v>
-      </c>
-      <c r="G61">
-        <v>4202220000</v>
-      </c>
+      <c r="B61" s=""/>
+      <c r="C61" s=""/>
+      <c r="D61" s=""/>
+      <c r="F61" s=""/>
+      <c r="G61" s=""/>
     </row>
     <row r="62" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
       <c r="I62" s="6"/>
-      <c r="B62">
-        <v>4900228258</v>
-      </c>
-      <c r="C62" t="s">
-        <v>74</v>
-      </c>
-      <c r="D62" t="s">
-        <v>66</v>
-      </c>
-      <c r="F62">
-        <v>61</v>
-      </c>
-      <c r="G62">
-        <v>4202220000</v>
-      </c>
+      <c r="B62" s=""/>
+      <c r="C62" s=""/>
+      <c r="D62" s=""/>
+      <c r="F62" s=""/>
+      <c r="G62" s=""/>
     </row>
     <row r="63" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
       <c r="I63" s="6"/>
-      <c r="B63">
-        <v>4900228258</v>
-      </c>
-      <c r="C63" t="s">
-        <v>75</v>
-      </c>
-      <c r="D63" t="s">
-        <v>66</v>
-      </c>
-      <c r="F63">
-        <v>61</v>
-      </c>
-      <c r="G63">
-        <v>4202220000</v>
-      </c>
+      <c r="B63" s=""/>
+      <c r="C63" s=""/>
+      <c r="D63" s=""/>
+      <c r="F63" s=""/>
+      <c r="G63" s=""/>
     </row>
     <row r="64" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
       <c r="I64" s="6"/>
-      <c r="B64">
-        <v>4900228258</v>
-      </c>
-      <c r="C64" t="s">
-        <v>76</v>
-      </c>
-      <c r="D64" t="s">
-        <v>77</v>
-      </c>
-      <c r="F64">
-        <v>20</v>
-      </c>
-      <c r="G64">
-        <v>4202220000</v>
-      </c>
+      <c r="B64" s=""/>
+      <c r="C64" s=""/>
+      <c r="D64" s=""/>
+      <c r="F64" s=""/>
+      <c r="G64" s=""/>
     </row>
     <row r="65" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
       <c r="I65" s="6"/>
-      <c r="B65">
-        <v>4900228258</v>
-      </c>
-      <c r="C65" t="s">
-        <v>78</v>
-      </c>
-      <c r="D65" t="s">
-        <v>77</v>
-      </c>
-      <c r="F65">
-        <v>69</v>
-      </c>
-      <c r="G65">
-        <v>4202220000</v>
-      </c>
+      <c r="B65" s=""/>
+      <c r="C65" s=""/>
+      <c r="D65" s=""/>
+      <c r="F65" s=""/>
+      <c r="G65" s=""/>
     </row>
     <row r="66" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
       <c r="I66" s="6"/>
-      <c r="B66">
-        <v>4900228258</v>
-      </c>
-      <c r="C66" t="s">
-        <v>79</v>
-      </c>
-      <c r="D66" t="s">
-        <v>77</v>
-      </c>
-      <c r="F66">
-        <v>32</v>
-      </c>
-      <c r="G66">
-        <v>4202220000</v>
-      </c>
+      <c r="B66" s=""/>
+      <c r="C66" s=""/>
+      <c r="D66" s=""/>
+      <c r="F66" s=""/>
+      <c r="G66" s=""/>
     </row>
     <row r="67" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A67" s="79"/>
       <c r="E67" s="39"/>
       <c r="H67" s="39"/>
       <c r="I67" s="40"/>
-      <c r="B67" s="39">
-        <v>4900228259</v>
-      </c>
-      <c r="C67" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="D67" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="F67" s="39">
-        <v>14</v>
-      </c>
-      <c r="G67" s="39">
-        <v>4202220000</v>
-      </c>
+      <c r="B67" s="39"/>
+      <c r="C67" s="39"/>
+      <c r="D67" s="39"/>
+      <c r="F67" s="39"/>
+      <c r="G67" s="39"/>
     </row>
     <row r="68" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
-      <c r="B68">
-        <v>4900228259</v>
-      </c>
-      <c r="C68" t="s">
-        <v>67</v>
-      </c>
-      <c r="D68" t="s">
-        <v>66</v>
-      </c>
-      <c r="F68">
-        <v>14</v>
-      </c>
-      <c r="G68">
-        <v>4202220000</v>
-      </c>
+      <c r="B68" s=""/>
+      <c r="C68" s=""/>
+      <c r="D68" s=""/>
+      <c r="F68" s=""/>
+      <c r="G68" s=""/>
     </row>
     <row r="69" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B69">
-        <v>4900228259</v>
-      </c>
-      <c r="C69" t="s">
-        <v>68</v>
-      </c>
-      <c r="D69" t="s">
-        <v>66</v>
-      </c>
-      <c r="F69">
-        <v>10</v>
-      </c>
-      <c r="G69">
-        <v>4202220000</v>
-      </c>
+      <c r="B69" s=""/>
+      <c r="C69" s=""/>
+      <c r="D69" s=""/>
+      <c r="F69" s=""/>
+      <c r="G69" s=""/>
     </row>
     <row r="70" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B70">
-        <v>4900228259</v>
-      </c>
-      <c r="C70" t="s">
-        <v>69</v>
-      </c>
-      <c r="D70" t="s">
-        <v>66</v>
-      </c>
-      <c r="F70">
-        <v>7</v>
-      </c>
-      <c r="G70">
-        <v>4202220000</v>
-      </c>
+      <c r="B70" s=""/>
+      <c r="C70" s=""/>
+      <c r="D70" s=""/>
+      <c r="F70" s=""/>
+      <c r="G70" s=""/>
     </row>
     <row r="71" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B71">
-        <v>4900228259</v>
-      </c>
-      <c r="C71" t="s">
-        <v>70</v>
-      </c>
-      <c r="D71" t="s">
-        <v>66</v>
-      </c>
-      <c r="F71">
-        <v>18</v>
-      </c>
-      <c r="G71">
-        <v>4202220000</v>
-      </c>
+      <c r="B71" s=""/>
+      <c r="C71" s=""/>
+      <c r="D71" s=""/>
+      <c r="F71" s=""/>
+      <c r="G71" s=""/>
     </row>
     <row r="72" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B72">
-        <v>4900228259</v>
-      </c>
-      <c r="C72" t="s">
-        <v>71</v>
-      </c>
-      <c r="D72" t="s">
-        <v>66</v>
-      </c>
-      <c r="F72">
-        <v>18</v>
-      </c>
-      <c r="G72">
-        <v>4202220000</v>
-      </c>
+      <c r="B72" s=""/>
+      <c r="C72" s=""/>
+      <c r="D72" s=""/>
+      <c r="F72" s=""/>
+      <c r="G72" s=""/>
     </row>
     <row r="73" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B73">
-        <v>4900228259</v>
-      </c>
-      <c r="C73" t="s">
-        <v>72</v>
-      </c>
-      <c r="D73" t="s">
-        <v>66</v>
-      </c>
-      <c r="F73">
-        <v>14</v>
-      </c>
-      <c r="G73">
-        <v>4202220000</v>
-      </c>
+      <c r="B73" s=""/>
+      <c r="C73" s=""/>
+      <c r="D73" s=""/>
+      <c r="F73" s=""/>
+      <c r="G73" s=""/>
     </row>
     <row r="74" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B74">
-        <v>4900228259</v>
-      </c>
-      <c r="C74" t="s">
-        <v>73</v>
-      </c>
-      <c r="D74" t="s">
-        <v>66</v>
-      </c>
-      <c r="F74">
-        <v>12</v>
-      </c>
-      <c r="G74">
-        <v>4202220000</v>
-      </c>
+      <c r="B74" s=""/>
+      <c r="C74" s=""/>
+      <c r="D74" s=""/>
+      <c r="F74" s=""/>
+      <c r="G74" s=""/>
     </row>
     <row r="75" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B75">
-        <v>4900228259</v>
-      </c>
-      <c r="C75" t="s">
-        <v>74</v>
-      </c>
-      <c r="D75" t="s">
-        <v>66</v>
-      </c>
-      <c r="F75">
-        <v>14</v>
-      </c>
-      <c r="G75">
-        <v>4202220000</v>
-      </c>
+      <c r="B75" s=""/>
+      <c r="C75" s=""/>
+      <c r="D75" s=""/>
+      <c r="F75" s=""/>
+      <c r="G75" s=""/>
     </row>
     <row r="76" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B76">
-        <v>4900228259</v>
-      </c>
-      <c r="C76" t="s">
-        <v>75</v>
-      </c>
-      <c r="D76" t="s">
-        <v>66</v>
-      </c>
-      <c r="F76">
-        <v>14</v>
-      </c>
-      <c r="G76">
-        <v>4202220000</v>
-      </c>
+      <c r="B76" s=""/>
+      <c r="C76" s=""/>
+      <c r="D76" s=""/>
+      <c r="F76" s=""/>
+      <c r="G76" s=""/>
     </row>
     <row r="77" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B77">
-        <v>4900228259</v>
-      </c>
-      <c r="C77" t="s">
-        <v>76</v>
-      </c>
-      <c r="D77" t="s">
-        <v>77</v>
-      </c>
-      <c r="F77">
-        <v>7</v>
-      </c>
-      <c r="G77">
-        <v>4202220000</v>
-      </c>
+      <c r="B77" s=""/>
+      <c r="C77" s=""/>
+      <c r="D77" s=""/>
+      <c r="F77" s=""/>
+      <c r="G77" s=""/>
     </row>
     <row r="78" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B78">
-        <v>4900228259</v>
-      </c>
-      <c r="C78" t="s">
-        <v>78</v>
-      </c>
-      <c r="D78" t="s">
-        <v>77</v>
-      </c>
-      <c r="F78">
-        <v>18</v>
-      </c>
-      <c r="G78">
-        <v>4202220000</v>
-      </c>
+      <c r="B78" s=""/>
+      <c r="C78" s=""/>
+      <c r="D78" s=""/>
+      <c r="F78" s=""/>
+      <c r="G78" s=""/>
     </row>
     <row r="79" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B79">
-        <v>4900228259</v>
-      </c>
-      <c r="C79" t="s">
-        <v>79</v>
-      </c>
-      <c r="D79" t="s">
-        <v>77</v>
-      </c>
-      <c r="F79">
-        <v>10</v>
-      </c>
-      <c r="G79">
-        <v>4202220000</v>
-      </c>
+      <c r="B79" s=""/>
+      <c r="C79" s=""/>
+      <c r="D79" s=""/>
+      <c r="F79" s=""/>
+      <c r="G79" s=""/>
     </row>
     <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" ht="19.9" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -2469,7 +2217,7 @@
       <c r="I93"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="36">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="A3:I3"/>
@@ -2504,6 +2252,8 @@
     <mergeCell ref="D53:E53"/>
     <mergeCell ref="H53:I53"/>
     <mergeCell ref="H93:I93"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>

--- a/templates/tpl_booking_mssnhsjl9u3s.xlsx
+++ b/templates/tpl_booking_mssnhsjl9u3s.xlsx
@@ -1935,224 +1935,484 @@
       <c r="E54" s="72"/>
       <c r="H54" s="73"/>
       <c r="I54" s="74"/>
-      <c r="B54" s="59"/>
-      <c r="C54" s=""/>
-      <c r="D54" s=""/>
-      <c r="F54" s=""/>
-      <c r="G54" s="61"/>
+      <c r="B54" s="59">
+        <v>4900228258</v>
+      </c>
+      <c r="C54" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54" t="s">
+        <v>66</v>
+      </c>
+      <c r="F54">
+        <v>61</v>
+      </c>
+      <c r="G54" s="61">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A55" s="71"/>
       <c r="E55" s="72"/>
       <c r="H55" s="73"/>
       <c r="I55" s="74"/>
-      <c r="B55" s="78"/>
-      <c r="C55" s="73"/>
-      <c r="D55" s="73"/>
-      <c r="F55" s="78"/>
-      <c r="G55" s="78"/>
+      <c r="B55" s="78">
+        <v>4900228258</v>
+      </c>
+      <c r="C55" s="73" t="s">
+        <v>67</v>
+      </c>
+      <c r="D55" s="73" t="s">
+        <v>66</v>
+      </c>
+      <c r="F55" s="78">
+        <v>61</v>
+      </c>
+      <c r="G55" s="78">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A56" s="41"/>
       <c r="E56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="4"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
+      <c r="B56" s="3">
+        <v>4900228258</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F56" s="3">
+        <v>20</v>
+      </c>
+      <c r="G56" s="3">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
       <c r="I57" s="6"/>
-      <c r="B57" s=""/>
-      <c r="C57" s=""/>
-      <c r="D57" s=""/>
-      <c r="F57" s=""/>
-      <c r="G57" s=""/>
+      <c r="B57">
+        <v>4900228258</v>
+      </c>
+      <c r="C57" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" t="s">
+        <v>66</v>
+      </c>
+      <c r="F57">
+        <v>18</v>
+      </c>
+      <c r="G57">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
       <c r="I58" s="6"/>
-      <c r="B58" s=""/>
-      <c r="C58" s=""/>
-      <c r="D58" s=""/>
-      <c r="F58" s=""/>
-      <c r="G58" s=""/>
+      <c r="B58">
+        <v>4900228258</v>
+      </c>
+      <c r="C58" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" t="s">
+        <v>66</v>
+      </c>
+      <c r="F58">
+        <v>69</v>
+      </c>
+      <c r="G58">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="59" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A59" s="79"/>
       <c r="E59" s="39"/>
       <c r="H59" s="39"/>
       <c r="I59" s="40"/>
-      <c r="B59" s="39"/>
-      <c r="C59" s="39"/>
-      <c r="D59" s="39"/>
-      <c r="F59" s="39"/>
-      <c r="G59" s="39"/>
+      <c r="B59" s="39">
+        <v>4900228258</v>
+      </c>
+      <c r="C59" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="D59" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="F59" s="39">
+        <v>69</v>
+      </c>
+      <c r="G59" s="39">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A60" s="41"/>
       <c r="E60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="4"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
+      <c r="B60" s="3">
+        <v>4900228258</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F60" s="3">
+        <v>61</v>
+      </c>
+      <c r="G60" s="3">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="I61" s="6"/>
-      <c r="B61" s=""/>
-      <c r="C61" s=""/>
-      <c r="D61" s=""/>
-      <c r="F61" s=""/>
-      <c r="G61" s=""/>
+      <c r="B61">
+        <v>4900228258</v>
+      </c>
+      <c r="C61" t="s">
+        <v>73</v>
+      </c>
+      <c r="D61" t="s">
+        <v>66</v>
+      </c>
+      <c r="F61">
+        <v>45</v>
+      </c>
+      <c r="G61">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
       <c r="I62" s="6"/>
-      <c r="B62" s=""/>
-      <c r="C62" s=""/>
-      <c r="D62" s=""/>
-      <c r="F62" s=""/>
-      <c r="G62" s=""/>
+      <c r="B62">
+        <v>4900228258</v>
+      </c>
+      <c r="C62" t="s">
+        <v>74</v>
+      </c>
+      <c r="D62" t="s">
+        <v>66</v>
+      </c>
+      <c r="F62">
+        <v>61</v>
+      </c>
+      <c r="G62">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
       <c r="I63" s="6"/>
-      <c r="B63" s=""/>
-      <c r="C63" s=""/>
-      <c r="D63" s=""/>
-      <c r="F63" s=""/>
-      <c r="G63" s=""/>
+      <c r="B63">
+        <v>4900228258</v>
+      </c>
+      <c r="C63" t="s">
+        <v>75</v>
+      </c>
+      <c r="D63" t="s">
+        <v>66</v>
+      </c>
+      <c r="F63">
+        <v>61</v>
+      </c>
+      <c r="G63">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
       <c r="I64" s="6"/>
-      <c r="B64" s=""/>
-      <c r="C64" s=""/>
-      <c r="D64" s=""/>
-      <c r="F64" s=""/>
-      <c r="G64" s=""/>
+      <c r="B64">
+        <v>4900228258</v>
+      </c>
+      <c r="C64" t="s">
+        <v>76</v>
+      </c>
+      <c r="D64" t="s">
+        <v>77</v>
+      </c>
+      <c r="F64">
+        <v>20</v>
+      </c>
+      <c r="G64">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
       <c r="I65" s="6"/>
-      <c r="B65" s=""/>
-      <c r="C65" s=""/>
-      <c r="D65" s=""/>
-      <c r="F65" s=""/>
-      <c r="G65" s=""/>
+      <c r="B65">
+        <v>4900228258</v>
+      </c>
+      <c r="C65" t="s">
+        <v>78</v>
+      </c>
+      <c r="D65" t="s">
+        <v>77</v>
+      </c>
+      <c r="F65">
+        <v>69</v>
+      </c>
+      <c r="G65">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="66" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
       <c r="I66" s="6"/>
-      <c r="B66" s=""/>
-      <c r="C66" s=""/>
-      <c r="D66" s=""/>
-      <c r="F66" s=""/>
-      <c r="G66" s=""/>
+      <c r="B66">
+        <v>4900228258</v>
+      </c>
+      <c r="C66" t="s">
+        <v>79</v>
+      </c>
+      <c r="D66" t="s">
+        <v>77</v>
+      </c>
+      <c r="F66">
+        <v>32</v>
+      </c>
+      <c r="G66">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="A67" s="79"/>
       <c r="E67" s="39"/>
       <c r="H67" s="39"/>
       <c r="I67" s="40"/>
-      <c r="B67" s="39"/>
-      <c r="C67" s="39"/>
-      <c r="D67" s="39"/>
-      <c r="F67" s="39"/>
-      <c r="G67" s="39"/>
+      <c r="B67" s="39">
+        <v>4900228259</v>
+      </c>
+      <c r="C67" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="D67" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="F67" s="39">
+        <v>14</v>
+      </c>
+      <c r="G67" s="39">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="68" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
-      <c r="B68" s=""/>
-      <c r="C68" s=""/>
-      <c r="D68" s=""/>
-      <c r="F68" s=""/>
-      <c r="G68" s=""/>
+      <c r="B68">
+        <v>4900228259</v>
+      </c>
+      <c r="C68" t="s">
+        <v>67</v>
+      </c>
+      <c r="D68" t="s">
+        <v>66</v>
+      </c>
+      <c r="F68">
+        <v>14</v>
+      </c>
+      <c r="G68">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="69" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B69" s=""/>
-      <c r="C69" s=""/>
-      <c r="D69" s=""/>
-      <c r="F69" s=""/>
-      <c r="G69" s=""/>
+      <c r="B69">
+        <v>4900228259</v>
+      </c>
+      <c r="C69" t="s">
+        <v>68</v>
+      </c>
+      <c r="D69" t="s">
+        <v>66</v>
+      </c>
+      <c r="F69">
+        <v>10</v>
+      </c>
+      <c r="G69">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B70" s=""/>
-      <c r="C70" s=""/>
-      <c r="D70" s=""/>
-      <c r="F70" s=""/>
-      <c r="G70" s=""/>
+      <c r="B70">
+        <v>4900228259</v>
+      </c>
+      <c r="C70" t="s">
+        <v>69</v>
+      </c>
+      <c r="D70" t="s">
+        <v>66</v>
+      </c>
+      <c r="F70">
+        <v>7</v>
+      </c>
+      <c r="G70">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B71" s=""/>
-      <c r="C71" s=""/>
-      <c r="D71" s=""/>
-      <c r="F71" s=""/>
-      <c r="G71" s=""/>
+      <c r="B71">
+        <v>4900228259</v>
+      </c>
+      <c r="C71" t="s">
+        <v>70</v>
+      </c>
+      <c r="D71" t="s">
+        <v>66</v>
+      </c>
+      <c r="F71">
+        <v>18</v>
+      </c>
+      <c r="G71">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B72" s=""/>
-      <c r="C72" s=""/>
-      <c r="D72" s=""/>
-      <c r="F72" s=""/>
-      <c r="G72" s=""/>
+      <c r="B72">
+        <v>4900228259</v>
+      </c>
+      <c r="C72" t="s">
+        <v>71</v>
+      </c>
+      <c r="D72" t="s">
+        <v>66</v>
+      </c>
+      <c r="F72">
+        <v>18</v>
+      </c>
+      <c r="G72">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="73" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B73" s=""/>
-      <c r="C73" s=""/>
-      <c r="D73" s=""/>
-      <c r="F73" s=""/>
-      <c r="G73" s=""/>
+      <c r="B73">
+        <v>4900228259</v>
+      </c>
+      <c r="C73" t="s">
+        <v>72</v>
+      </c>
+      <c r="D73" t="s">
+        <v>66</v>
+      </c>
+      <c r="F73">
+        <v>14</v>
+      </c>
+      <c r="G73">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B74" s=""/>
-      <c r="C74" s=""/>
-      <c r="D74" s=""/>
-      <c r="F74" s=""/>
-      <c r="G74" s=""/>
+      <c r="B74">
+        <v>4900228259</v>
+      </c>
+      <c r="C74" t="s">
+        <v>73</v>
+      </c>
+      <c r="D74" t="s">
+        <v>66</v>
+      </c>
+      <c r="F74">
+        <v>12</v>
+      </c>
+      <c r="G74">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B75" s=""/>
-      <c r="C75" s=""/>
-      <c r="D75" s=""/>
-      <c r="F75" s=""/>
-      <c r="G75" s=""/>
+      <c r="B75">
+        <v>4900228259</v>
+      </c>
+      <c r="C75" t="s">
+        <v>74</v>
+      </c>
+      <c r="D75" t="s">
+        <v>66</v>
+      </c>
+      <c r="F75">
+        <v>14</v>
+      </c>
+      <c r="G75">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B76" s=""/>
-      <c r="C76" s=""/>
-      <c r="D76" s=""/>
-      <c r="F76" s=""/>
-      <c r="G76" s=""/>
+      <c r="B76">
+        <v>4900228259</v>
+      </c>
+      <c r="C76" t="s">
+        <v>75</v>
+      </c>
+      <c r="D76" t="s">
+        <v>66</v>
+      </c>
+      <c r="F76">
+        <v>14</v>
+      </c>
+      <c r="G76">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="77" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B77" s=""/>
-      <c r="C77" s=""/>
-      <c r="D77" s=""/>
-      <c r="F77" s=""/>
-      <c r="G77" s=""/>
+      <c r="B77">
+        <v>4900228259</v>
+      </c>
+      <c r="C77" t="s">
+        <v>76</v>
+      </c>
+      <c r="D77" t="s">
+        <v>77</v>
+      </c>
+      <c r="F77">
+        <v>7</v>
+      </c>
+      <c r="G77">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="78" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B78" s=""/>
-      <c r="C78" s=""/>
-      <c r="D78" s=""/>
-      <c r="F78" s=""/>
-      <c r="G78" s=""/>
+      <c r="B78">
+        <v>4900228259</v>
+      </c>
+      <c r="C78" t="s">
+        <v>78</v>
+      </c>
+      <c r="D78" t="s">
+        <v>77</v>
+      </c>
+      <c r="F78">
+        <v>18</v>
+      </c>
+      <c r="G78">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="79" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B79" s=""/>
-      <c r="C79" s=""/>
-      <c r="D79" s=""/>
-      <c r="F79" s=""/>
-      <c r="G79" s=""/>
+      <c r="B79">
+        <v>4900228259</v>
+      </c>
+      <c r="C79" t="s">
+        <v>79</v>
+      </c>
+      <c r="D79" t="s">
+        <v>77</v>
+      </c>
+      <c r="F79">
+        <v>10</v>
+      </c>
+      <c r="G79">
+        <v>4202220000</v>
+      </c>
     </row>
     <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" ht="19.9" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
